--- a/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E8A32A-0C6F-4938-9321-9ADC428A92D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD0FB5-1947-4DD4-BB47-B43D68D91140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,13 +56,13 @@
     <t>Attribute</t>
   </si>
   <si>
-    <t>NCAP_BND</t>
-  </si>
-  <si>
     <t>LimType</t>
   </si>
   <si>
     <t>LO</t>
+  </si>
+  <si>
+    <t>CAP_BND</t>
   </si>
 </sst>
 </file>
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>2030</v>
@@ -426,10 +426,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>2</v>

--- a/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD0FB5-1947-4DD4-BB47-B43D68D91140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB3C8E-AE26-439E-B463-68EA6E0E99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,46 +36,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>~TFM_INS-TS</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>EST</t>
   </si>
   <si>
-    <t>coal,gas,nuclear,bioenergy</t>
-  </si>
-  <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>Attribute</t>
-  </si>
-  <si>
     <t>LimType</t>
   </si>
   <si>
     <t>LO</t>
   </si>
   <si>
-    <t>CAP_BND</t>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T:UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UC_min_solid_2035</t>
+  </si>
+  <si>
+    <t>pp_controllable</t>
+  </si>
+  <si>
+    <t>Minimum solid fuel power plants penetration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,8 +122,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,68 +405,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:I5"/>
+  <dimension ref="B3:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
         <v>0</v>
       </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>2030</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>2030</v>
-      </c>
-      <c r="G4">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
         <v>2035</v>
       </c>
-      <c r="H4">
-        <v>2040</v>
-      </c>
-      <c r="I4">
-        <v>2050</v>
+      <c r="F8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2.1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2.1</v>
-      </c>
-      <c r="H5">
-        <v>2.1</v>
-      </c>
-      <c r="I5">
-        <v>2.1</v>
+      <c r="H9">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB3C8E-AE26-439E-B463-68EA6E0E99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F3835F-325C-4E53-9E8E-0F4A3BE5DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,10 +77,10 @@
     <t>UC_min_solid_2035</t>
   </si>
   <si>
-    <t>pp_controllable</t>
-  </si>
-  <si>
     <t>Minimum solid fuel power plants penetration</t>
+  </si>
+  <si>
+    <t>pp_controllable,Util Batt Stg</t>
   </si>
 </sst>
 </file>
@@ -408,8 +408,8 @@
   <dimension ref="B3:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -456,7 +456,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>2030</v>
@@ -471,12 +471,12 @@
         <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>2035</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>0</v>

--- a/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F3835F-325C-4E53-9E8E-0F4A3BE5DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAD28D4-1BA6-44BC-9B0E-374FD13ACA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="s">
         <v>13</v>

--- a/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_min_controllable_capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAD28D4-1BA6-44BC-9B0E-374FD13ACA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9288F465-56FD-4989-990C-3267375136B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,21 +96,65 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="186"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,16 +162,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 4" xfId="1" xr:uid="{90EB05A0-5DDA-48CC-B828-EBEA9B64AE72}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -405,53 +477,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:J9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>12</v>
       </c>
@@ -474,7 +548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>14</v>
       </c>
@@ -491,7 +565,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>14</v>
       </c>
